--- a/artfynd/A 29532-2022 artfynd.xlsx
+++ b/artfynd/A 29532-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29532-2022 artfynd.xlsx
+++ b/artfynd/A 29532-2022 artfynd.xlsx
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>

--- a/artfynd/A 29532-2022 artfynd.xlsx
+++ b/artfynd/A 29532-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>1103025</v>
       </c>
       <c r="B2" t="n">
-        <v>85001</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Corner</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539682.2096451229</v>
+        <v>539682</v>
       </c>
       <c r="R2" t="n">
-        <v>6642981.141261848</v>
+        <v>6642981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2009-09-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,6 +782,122 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5387503</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101794</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222929</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Backruta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Thalictrum simplex</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Moren,  strax norr om sjön Dagarns norra spets, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>539671</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6642956</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1988-07-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1988-07-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Dellokal 2 - riklig på ängsartad åkerholme.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Rikkärr</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 29532-2022 artfynd.xlsx
+++ b/artfynd/A 29532-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1103025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,8 +910,17 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5387503</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>